--- a/outputs/tables/tab-2-unidades.xlsx
+++ b/outputs/tables/tab-2-unidades.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,14 +384,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Escola de Enfermagem</t>
+          <t>Faculdade de Odontologia de Bauru</t>
         </is>
       </c>
       <c r="C2">
-        <v>1071</v>
+        <v>824</v>
       </c>
       <c r="D2">
-        <v>0.361344537815126</v>
+        <v>0.433252427184466</v>
       </c>
     </row>
     <row r="3">
@@ -402,14 +402,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Faculdade de Odontologia de Bauru</t>
+          <t>Escola de Enfermagem</t>
         </is>
       </c>
       <c r="C3">
-        <v>1439</v>
+        <v>741</v>
       </c>
       <c r="D3">
-        <v>0.3564975677553857</v>
+        <v>0.4048582995951417</v>
       </c>
     </row>
     <row r="4">
@@ -424,28 +424,28 @@
         </is>
       </c>
       <c r="C4">
-        <v>1098</v>
+        <v>767</v>
       </c>
       <c r="D4">
-        <v>0.3306010928961748</v>
+        <v>0.3989569752281616</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Ciências da Saúde</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Instituto de Arquitetura e Urbanismo de São Carlos</t>
+          <t>Faculdade de Ciências Farmacêuticas de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C5">
-        <v>575</v>
+        <v>754</v>
       </c>
       <c r="D5">
-        <v>0.3286956521739131</v>
+        <v>0.3488063660477453</v>
       </c>
     </row>
     <row r="6">
@@ -456,14 +456,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Faculdade de Ciências Farmacêuticas de Ribeirão Preto</t>
+          <t>Escola de Enfermagem de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C6">
-        <v>1092</v>
+        <v>1184</v>
       </c>
       <c r="D6">
-        <v>0.304945054945055</v>
+        <v>0.347972972972973</v>
       </c>
     </row>
     <row r="7">
@@ -474,14 +474,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Escola de Enfermagem de Ribeirão Preto</t>
+          <t>Faculdade de Odontologia de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C7">
-        <v>1764</v>
+        <v>730</v>
       </c>
       <c r="D7">
-        <v>0.2959183673469388</v>
+        <v>0.3479452054794521</v>
       </c>
     </row>
     <row r="8">
@@ -492,104 +492,104 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Faculdade de Odontologia de Ribeirão Preto</t>
+          <t>Faculdade de Odontologia</t>
         </is>
       </c>
       <c r="C8">
-        <v>1051</v>
+        <v>1214</v>
       </c>
       <c r="D8">
-        <v>0.2892483349191247</v>
+        <v>0.329489291598023</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Ciências Humanas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Faculdade de Odontologia</t>
+          <t>Instituto de Psicologia</t>
         </is>
       </c>
       <c r="C9">
-        <v>1766</v>
+        <v>683</v>
       </c>
       <c r="D9">
-        <v>0.2729331823329558</v>
+        <v>0.2869692532942899</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ciências Biológicas</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Instituto de Ciências Biomédicas</t>
+          <t>Faculdade de Zootecnia e Engenharia de Alimentos</t>
         </is>
       </c>
       <c r="C10">
-        <v>552</v>
+        <v>2476</v>
       </c>
       <c r="D10">
-        <v>0.2681159420289855</v>
+        <v>0.2742326332794831</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Ciências da Saúde</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Instituto Oceanográfico</t>
+          <t>Faculdade de Medicina de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C11">
-        <v>545</v>
+        <v>2134</v>
       </c>
       <c r="D11">
-        <v>0.255045871559633</v>
+        <v>0.2577319587628866</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Ciências da Saúde</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Instituto de Psicologia</t>
+          <t>Faculdade de Medicina</t>
         </is>
       </c>
       <c r="C12">
-        <v>977</v>
+        <v>2299</v>
       </c>
       <c r="D12">
-        <v>0.2425793244626407</v>
+        <v>0.2396694214876033</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Faculdade de Zootecnia e Engenharia de Alimentos</t>
+          <t>Instituto de Química de São Carlos</t>
         </is>
       </c>
       <c r="C13">
-        <v>3574</v>
+        <v>558</v>
       </c>
       <c r="D13">
-        <v>0.2386681589255736</v>
+        <v>0.2293906810035842</v>
       </c>
     </row>
     <row r="14">
@@ -600,32 +600,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Faculdade de Medicina</t>
+          <t>Faculdade de Ciências Farmacêuticas</t>
         </is>
       </c>
       <c r="C14">
-        <v>3327</v>
+        <v>1367</v>
       </c>
       <c r="D14">
-        <v>0.2224226029455966</v>
+        <v>0.2172640819312363</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Instituto de Química de São Carlos</t>
+          <t>Faculdade de Arquitetura e Urbanismo</t>
         </is>
       </c>
       <c r="C15">
-        <v>809</v>
+        <v>1803</v>
       </c>
       <c r="D15">
-        <v>0.211372064276885</v>
+        <v>0.2146422628951747</v>
       </c>
     </row>
     <row r="16">
@@ -636,122 +636,122 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Faculdade de Medicina de Ribeirão Preto</t>
+          <t>Faculdade de Saúde Pública</t>
         </is>
       </c>
       <c r="C16">
-        <v>3204</v>
+        <v>1051</v>
       </c>
       <c r="D16">
-        <v>0.2063046192259675</v>
+        <v>0.2093244529019981</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Ciências Biológicas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Faculdade de Ciências Farmacêuticas</t>
+          <t>Instituto de Biociências</t>
         </is>
       </c>
       <c r="C17">
-        <v>1974</v>
+        <v>1136</v>
       </c>
       <c r="D17">
-        <v>0.2041540020263425</v>
+        <v>0.2015845070422535</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Faculdade de Arquitetura e Urbanismo</t>
+          <t>Instituto de Astronomia, Geofísica e Ciências Atmosféricas</t>
         </is>
       </c>
       <c r="C18">
-        <v>2624</v>
+        <v>804</v>
       </c>
       <c r="D18">
-        <v>0.2023628048780488</v>
+        <v>0.1977611940298507</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Faculdade de Saúde Pública</t>
+          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C19">
-        <v>1565</v>
+        <v>3606</v>
       </c>
       <c r="D19">
-        <v>0.1846645367412141</v>
+        <v>0.1758180809761509</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ciências Biológicas</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Instituto de Biociências</t>
+          <t>Instituto de Química</t>
         </is>
       </c>
       <c r="C20">
-        <v>1654</v>
+        <v>1239</v>
       </c>
       <c r="D20">
-        <v>0.1777509068923821</v>
+        <v>0.1719128329297821</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Instituto de Astronomia, Geofísica e Ciências Atmosféricas</t>
+          <t>Escola Superior de Agricultura "Luiz de Queiroz"</t>
         </is>
       </c>
       <c r="C21">
-        <v>1165</v>
+        <v>3899</v>
       </c>
       <c r="D21">
-        <v>0.1639484978540773</v>
+        <v>0.164657604513978</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto</t>
+          <t>Escola de Engenharia de São Carlos</t>
         </is>
       </c>
       <c r="C22">
-        <v>5372</v>
+        <v>4219</v>
       </c>
       <c r="D22">
-        <v>0.1498510796723753</v>
+        <v>0.1616496800189618</v>
       </c>
     </row>
     <row r="23">
@@ -762,212 +762,212 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Instituto de Química</t>
+          <t>Instituto de Física de São Carlos</t>
         </is>
       </c>
       <c r="C23">
-        <v>1780</v>
+        <v>1190</v>
       </c>
       <c r="D23">
-        <v>0.1438202247191011</v>
+        <v>0.1453781512605042</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Escola Superior de Agricultura "Luiz de Queiroz"</t>
+          <t>Escola Politécnica</t>
         </is>
       </c>
       <c r="C24">
-        <v>5696</v>
+        <v>7932</v>
       </c>
       <c r="D24">
-        <v>0.1404494382022472</v>
+        <v>0.1429652042360061</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Ciências da Saúde</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Instituto de Relações Internacionais</t>
+          <t>Escola de Educação Física e Esporte de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C25">
-        <v>846</v>
+        <v>581</v>
       </c>
       <c r="D25">
-        <v>0.1382978723404255</v>
+        <v>0.1411359724612737</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Instituto de Física de São Carlos</t>
+          <t>Instituto de Relações Internacionais</t>
         </is>
       </c>
       <c r="C26">
-        <v>1712</v>
+        <v>589</v>
       </c>
       <c r="D26">
-        <v>0.1378504672897196</v>
+        <v>0.134125636672326</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Escola de Engenharia de São Carlos</t>
+          <t>Escola de Engenharia de São Carlos e Instituto de Ciências Matemáticas e de Computação</t>
         </is>
       </c>
       <c r="C27">
-        <v>6020</v>
+        <v>557</v>
       </c>
       <c r="D27">
-        <v>0.1368770764119601</v>
+        <v>0.1310592459605027</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências da Saúde</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Escola Politécnica</t>
+          <t>Escola de Educação Física e Esporte</t>
         </is>
       </c>
       <c r="C28">
-        <v>11518</v>
+        <v>992</v>
       </c>
       <c r="D28">
-        <v>0.1309255079006772</v>
+        <v>0.123991935483871</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Escola de Engenharia de São Carlos e Instituto de Ciências Matemáticas e de Computação</t>
+          <t>Escola de Engenharia de Lorena</t>
         </is>
       </c>
       <c r="C29">
-        <v>768</v>
+        <v>2997</v>
       </c>
       <c r="D29">
-        <v>0.12109375</v>
+        <v>0.1234567901234568</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Humanas</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Escola de Engenharia de Lorena</t>
+          <t>Faculdade de Filosofia, Letras e Ciências Humanas</t>
         </is>
       </c>
       <c r="C30">
-        <v>4408</v>
+        <v>15460</v>
       </c>
       <c r="D30">
-        <v>0.1200090744101633</v>
+        <v>0.1131953428201811</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Escola de Educação Física e Esporte de Ribeirão Preto</t>
+          <t>Instituto de Geociências</t>
         </is>
       </c>
       <c r="C31">
-        <v>839</v>
+        <v>933</v>
       </c>
       <c r="D31">
-        <v>0.1156138259833135</v>
+        <v>0.1114683815648446</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Escola de Educação Física e Esporte</t>
+          <t>Faculdade de Direito de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C32">
-        <v>1424</v>
+        <v>981</v>
       </c>
       <c r="D32">
-        <v>0.1053370786516854</v>
+        <v>0.1100917431192661</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Faculdade de Filosofia, Letras e Ciências Humanas</t>
+          <t>Faculdade de Economia, Administração e Contabilidade de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C33">
-        <v>22220</v>
+        <v>2487</v>
       </c>
       <c r="D33">
-        <v>0.1003600360036004</v>
+        <v>0.1073582629674306</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Faculdade de Direito de Ribeirão Preto</t>
+          <t>Instituto de Física</t>
         </is>
       </c>
       <c r="C34">
-        <v>1431</v>
+        <v>2895</v>
       </c>
       <c r="D34">
-        <v>0.09923130677847659</v>
+        <v>0.09844559585492228</v>
       </c>
     </row>
     <row r="35">
@@ -978,104 +978,104 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Instituto de Física</t>
+          <t>Instituto de Ciências Matemáticas e de Computação</t>
         </is>
       </c>
       <c r="C35">
-        <v>4138</v>
+        <v>2538</v>
       </c>
       <c r="D35">
-        <v>0.0985983566940551</v>
+        <v>0.08353033884948778</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Ciências Humanas</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Instituto de Geociências</t>
+          <t>Faculdade de Educação</t>
         </is>
       </c>
       <c r="C36">
-        <v>1348</v>
+        <v>1811</v>
       </c>
       <c r="D36">
-        <v>0.0956973293768546</v>
+        <v>0.08227498619547212</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Linguística, Letras e Artes</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Faculdade de Economia, Administração e Contabilidade de Ribeirão Preto</t>
+          <t>Escola de Comunicações e Artes</t>
         </is>
       </c>
       <c r="C37">
-        <v>3588</v>
+        <v>3854</v>
       </c>
       <c r="D37">
-        <v>0.08946488294314381</v>
+        <v>0.07576543850544888</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Instituto de Ciências Matemáticas e de Computação</t>
+          <t>Escola de Artes, Ciências e Humanidades</t>
         </is>
       </c>
       <c r="C38">
-        <v>3694</v>
+        <v>9386</v>
       </c>
       <c r="D38">
-        <v>0.07958852192744992</v>
+        <v>0.0552951203920733</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Linguística, Letras e Artes</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Escola de Comunicações e Artes</t>
+          <t>Faculdade de Economia, Administração, Contabilidade e Atuária</t>
         </is>
       </c>
       <c r="C39">
-        <v>5631</v>
+        <v>5849</v>
       </c>
       <c r="D39">
-        <v>0.06925945657964838</v>
+        <v>0.05146178833988716</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Faculdade de Educação</t>
+          <t>Faculdade de Direito</t>
         </is>
       </c>
       <c r="C40">
-        <v>2623</v>
+        <v>4251</v>
       </c>
       <c r="D40">
-        <v>0.0670987418985894</v>
+        <v>0.04587155963302753</v>
       </c>
     </row>
     <row r="41">
@@ -1086,104 +1086,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Escola de Artes, Ciências e Humanidades</t>
+          <t>Pró-reitoria de Graduação</t>
         </is>
       </c>
       <c r="C41">
-        <v>13479</v>
+        <v>1291</v>
       </c>
       <c r="D41">
-        <v>0.05111655167297277</v>
+        <v>0.03795507358636716</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Faculdade de Economia, Administração, Contabilidade e Atuária</t>
+          <t>Instituto de Matemática e Estatística</t>
         </is>
       </c>
       <c r="C42">
-        <v>8341</v>
+        <v>3697</v>
       </c>
       <c r="D42">
-        <v>0.04711665267953483</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Multidisciplinar</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Pró-reitoria de Graduação</t>
-        </is>
-      </c>
-      <c r="C43">
-        <v>1419</v>
-      </c>
-      <c r="D43">
-        <v>0.04228329809725159</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Ciências Sociais Aplicadas</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Faculdade de Direito</t>
-        </is>
-      </c>
-      <c r="C44">
-        <v>6180</v>
-      </c>
-      <c r="D44">
-        <v>0.04142394822006473</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Ciências Exatas e da Terra</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Instituto de Matemática e Estatística</t>
-        </is>
-      </c>
-      <c r="C45">
-        <v>5299</v>
-      </c>
-      <c r="D45">
-        <v>0.02981694659369693</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Multidisciplinar</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Interunidades de Licenciatura IFSC/IQSC/ICMC</t>
-        </is>
-      </c>
-      <c r="C46">
-        <v>588</v>
-      </c>
-      <c r="D46">
-        <v>0.0272108843537415</v>
+        <v>0.02948336489045172</v>
       </c>
     </row>
   </sheetData>
